--- a/docs/downloads/11/tbl_cata_type_alaotra_mangabe.xlsx
+++ b/docs/downloads/11/tbl_cata_type_alaotra_mangabe.xlsx
@@ -477,12 +477,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>5.5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +489,6 @@
           <t>Maladie des cultures/élevage</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>5.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +501,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +513,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -711,12 +687,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -729,12 +699,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -746,12 +710,6 @@
         <is>
           <t>Criquets</t>
         </is>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>
